--- a/services/guide_service/data/dustbins_with_types.xlsx
+++ b/services/guide_service/data/dustbins_with_types.xlsx
@@ -431,19 +431,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>站点名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>经度</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>纬度</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>站点名称</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>其他</t>
@@ -466,33 +466,41 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>22号楼南侧</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>116.338829</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>39.94951</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>22号楼南侧</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2号宿舍楼前</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>116.340091</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>39.949162</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2号宿舍楼前</t>
-        </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -508,79 +516,91 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>南门小树林西南侧</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>116.340865</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" t="n">
         <v>39.949415</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>南门小树林西南侧</t>
-        </is>
-      </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>排球场前</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>116.339867</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>39.949656</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>排球场前</t>
-        </is>
-      </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>九教南</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>116.34253</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" t="n">
         <v>39.949534</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>九教南</t>
-        </is>
-      </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12号宿舍楼前</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>116.339704</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>39.949757</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>12号宿舍楼前</t>
-        </is>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -596,79 +616,91 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>学四门口</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>116.343846</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" t="n">
         <v>39.949754</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>学四门口</t>
-        </is>
-      </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>九教西侧</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>116.341436</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>39.949641</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>九教西侧</t>
-        </is>
-      </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>九教东</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>116.343039</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>39.950212</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>九教东</t>
-        </is>
-      </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>留园餐厅前</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>116.34414</v>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" t="n">
         <v>39.950016</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>留园餐厅前</t>
-        </is>
       </c>
       <c r="D11" t="n">
         <v>4</v>
@@ -684,73 +716,91 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>南门小树林东北角</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>116.340169</v>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>39.949656</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>排球场内</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>快递柜旁菜鸟驿站</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>116.342694</v>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>39.950428</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>梧桐大道东侧</t>
-        </is>
-      </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>南门小树林东南角</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>116.344367</v>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" t="n">
         <v>39.950422</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>教工餐厅南侧</t>
-        </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>菜鸟驿站-快递柜旁</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>116.338738</v>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>39.950321</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>学生活动服务中心前</t>
-        </is>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -758,75 +808,99 @@
       <c r="E15" t="n">
         <v>1</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>菜鸟裹裹-取件柜旁</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>116.343545</v>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" t="n">
         <v>39.950688</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>红果园宾馆北门口</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>菜鸟-取件柜旁</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>116.340386</v>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" t="n">
         <v>39.950419</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>积秀园</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>小树林东南角菜鸟</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>116.337546</v>
       </c>
-      <c r="B18" t="n">
+      <c r="C18" t="n">
         <v>39.951113</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>西餐厅门口</t>
-        </is>
-      </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15号宿舍楼前</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>116.339327</v>
       </c>
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>39.951085</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>15号宿舍楼旁</t>
-        </is>
       </c>
       <c r="D19" t="n">
         <v>4</v>
@@ -842,172 +916,216 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>菜鸟驿站-小树林东</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>116.344036</v>
       </c>
-      <c r="B20" t="n">
+      <c r="C20" t="n">
         <v>39.950953</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>红果园餐厅北侧</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
       <c r="F20" t="n">
         <v>4</v>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>篮球场旁菜鸟柜</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>116.339925</v>
       </c>
-      <c r="B21" t="n">
+      <c r="C21" t="n">
         <v>39.951079</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>思源西楼前</t>
-        </is>
-      </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>篮球场旁取件柜</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>116.340389</v>
       </c>
-      <c r="B22" t="n">
+      <c r="C22" t="n">
         <v>39.950979</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>思源楼前</t>
-        </is>
-      </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>篮球场旁</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>116.338569</v>
       </c>
-      <c r="B23" t="n">
+      <c r="C23" t="n">
         <v>39.952282</v>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>西操东</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>快递3号楼-篮球场</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>116.34312</v>
       </c>
-      <c r="B24" t="n">
+      <c r="C24" t="n">
         <v>39.951148</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>芳华园西侧</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>菜鸟驿站-图书馆旁</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>116.3462</v>
       </c>
-      <c r="B25" t="n">
+      <c r="C25" t="n">
         <v>39.950759</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>机械工程楼前</t>
-        </is>
-      </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>菜鸟柜-图书馆旁</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>116.341042</v>
       </c>
-      <c r="B26" t="n">
+      <c r="C26" t="n">
         <v>39.952259</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>二号教学楼东南侧</t>
-        </is>
-      </c>
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>取件柜-图书馆旁</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>116.34131</v>
       </c>
-      <c r="B27" t="n">
+      <c r="C27" t="n">
         <v>39.952285</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>一号教学楼西北侧</t>
-        </is>
-      </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>22号楼旁菜鸟</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>116.338648</v>
       </c>
-      <c r="B28" t="n">
+      <c r="C28" t="n">
         <v>39.94997</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>22号楼楼前</t>
-        </is>
       </c>
       <c r="D28" t="n">
         <v>4</v>
@@ -1023,157 +1141,191 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>17号宿舍楼-取件柜旁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>116.339318</v>
       </c>
-      <c r="B29" t="n">
+      <c r="C29" t="n">
         <v>39.95143</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>17号教学楼门口</t>
-        </is>
-      </c>
       <c r="D29" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>5号教学楼-取件柜</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>116.342521</v>
       </c>
-      <c r="B30" t="n">
+      <c r="C30" t="n">
         <v>39.951395</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>5号教学楼北侧</t>
-        </is>
-      </c>
       <c r="D30" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>快递柜1|2|3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>116.343282</v>
       </c>
-      <c r="B31" t="n">
+      <c r="C31" t="n">
         <v>39.951751</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>图书馆前</t>
-        </is>
-      </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>快递3号楼-取件柜</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>116.343872</v>
       </c>
-      <c r="B32" t="n">
+      <c r="C32" t="n">
         <v>39.951363</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>芳华园东侧</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>南门小树林西北侧菜鸟柜</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>116.344847</v>
       </c>
-      <c r="B33" t="n">
+      <c r="C33" t="n">
         <v>39.951308</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>电气工程楼西门</t>
-        </is>
-      </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>南门菜鸟柜包裹代收点</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>116.337092</v>
       </c>
-      <c r="B34" t="n">
+      <c r="C34" t="n">
         <v>39.951154</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>西门外卖柜旁</t>
-        </is>
-      </c>
       <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>南门菜鸟柜取件柜旁</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>116.344372</v>
       </c>
-      <c r="B35" t="n">
+      <c r="C35" t="n">
         <v>39.951487</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>逸夫楼西门口</t>
-        </is>
-      </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>23号楼前</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>116.3465</v>
       </c>
-      <c r="B36" t="n">
+      <c r="C36" t="n">
         <v>39.95179</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>23号楼前</t>
-        </is>
       </c>
       <c r="D36" t="n">
         <v>2</v>
@@ -1189,33 +1341,41 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>取件柜2号|取件柜</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>116.337322</v>
       </c>
-      <c r="B37" t="n">
+      <c r="C37" t="n">
         <v>39.951707</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>体育馆东</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>菜鸟驿站-学生服务中心旁</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
         <v>116.345289</v>
       </c>
-      <c r="B38" t="n">
+      <c r="C38" t="n">
         <v>39.951958</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>研究生院门口</t>
-        </is>
       </c>
       <c r="D38" t="n">
         <v>2</v>
@@ -1223,71 +1383,99 @@
       <c r="E38" t="n">
         <v>2</v>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>篮球场旁</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
         <v>116.338376</v>
       </c>
-      <c r="B39" t="n">
+      <c r="C39" t="n">
         <v>39.951648</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>西操内</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>留园旁</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
         <v>116.344546</v>
       </c>
-      <c r="B40" t="n">
+      <c r="C40" t="n">
         <v>39.952318</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>东操场</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>留园取件柜</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
         <v>116.340902</v>
       </c>
-      <c r="B41" t="n">
+      <c r="C41" t="n">
         <v>39.952077</v>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>思源楼北</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>18号宿舍楼前</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
         <v>116.343492</v>
       </c>
-      <c r="B42" t="n">
+      <c r="C42" t="n">
         <v>39.952502</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>18号宿舍楼前</t>
-        </is>
       </c>
       <c r="D42" t="n">
         <v>4</v>
@@ -1303,16 +1491,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16号宿舍楼前</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
         <v>116.343676</v>
       </c>
-      <c r="B43" t="n">
+      <c r="C43" t="n">
         <v>39.953437</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>16号宿舍楼前</t>
-        </is>
       </c>
       <c r="D43" t="n">
         <v>5</v>
@@ -1320,25 +1508,37 @@
       <c r="E43" t="n">
         <v>1</v>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>取件柜-篮球场旁</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
         <v>116.341864</v>
       </c>
-      <c r="B44" t="n">
+      <c r="C44" t="n">
         <v>39.952125</v>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>科学会堂北</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
